--- a/03-salgado-public-fedramp-20x/artifacts/ksi_validation_register.xlsx
+++ b/03-salgado-public-fedramp-20x/artifacts/ksi_validation_register.xlsx
@@ -521,6 +521,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1463,6 +1464,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="11">
       <c r="A4" s="14" t="inlineStr">
         <is>
@@ -1548,7 +1550,7 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
@@ -1595,7 +1597,7 @@
       </c>
       <c r="H6" s="15" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="I6" s="15" t="inlineStr">
@@ -1639,6 +1641,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="11">
       <c r="A4" s="16" t="inlineStr">
         <is>
@@ -1828,6 +1831,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="23.85" customHeight="1" s="11">
       <c r="A3" s="17" t="inlineStr">
         <is>
